--- a/Result/profitability/3004.xlsx
+++ b/Result/profitability/3004.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.385</v>
+        <v>1.4825</v>
       </c>
       <c r="N2" t="n">
-        <v>25.66</v>
+        <v>25.27875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>1.22875</v>
+        <v>1.2475</v>
       </c>
       <c r="N3" t="n">
-        <v>25.8875</v>
+        <v>25.2675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03875</v>
+        <v>1.05125</v>
       </c>
       <c r="N4" t="n">
-        <v>25.705</v>
+        <v>25.08375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-4.86</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1825</v>
+        <v>0.2987499999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>17.21375</v>
+        <v>17.01</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009999999999999978</v>
+        <v>0.1149999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>16.87625</v>
+        <v>17.19625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>-0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2575</v>
+        <v>-0.1850000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>16.33625</v>
+        <v>16.1875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.43625</v>
+        <v>-0.4150000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>16.47125</v>
+        <v>16.21625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>1.07</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5425</v>
+        <v>-0.5425000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>17.9725</v>
@@ -1649,7 +1649,7 @@
         <v>1.04</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4125</v>
+        <v>-0.4125000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>18.75375</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3325</v>
+        <v>-0.3325000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>19.425</v>
@@ -1903,7 +1903,7 @@
         <v>0.93</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.26875</v>
+        <v>-0.2687500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>20.34125</v>
@@ -2030,7 +2030,7 @@
         <v>0.77</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>29.685</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1386</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1064</v>
+      </c>
+      <c r="E75" t="n">
+        <v>322</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>173</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.49%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>155</v>
+      </c>
+      <c r="K75" t="n">
+        <v>135</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.64625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.08854166666666674</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08082408874801894</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8017241379310345</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.629999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06564639548932738</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
